--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-01-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -448,24 +448,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>רובי וויליאמס הודה בכנות שהוא מעכב את יציאת האלבום בגלל שאינו רוצה להתחרות ב־The Life of a Showgirl של טיילור סוויפט. כעת האלבום הופיע לפתע, ללא הסבר, שבועיים בלבד לתוך ינואר, ככל הנראה משום שלוויליאמס יהיו פחות מתחרים במצעד האלבומים</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>רובי ויליאמס Britpop</v>
       </c>
     </row>
@@ -483,24 +486,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>את ההופעה הזו קיבלתי ביוטיוב (*), שיטה יעילה למי שנפשו לא חשקה לשרך דרכו למועדונים בלילות הקרים. הוידיאו נשלח לרגל יציאת אלבומו "תור זהבי", ששיר הנושא הוא ראפ עצבני בניחוח מזרחי, שיר אגו ביקורתי, אירוני ומודע לעצמו מלא בדאחקות, הגזמות,</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>עוז זהבי תור זהבי</v>
       </c>
     </row>
@@ -518,24 +524,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>האלבום של פטריק סבג אינו אוסף שירים אקראי, אלא מרחב. מקום לשהות בו.  נכנסים, שומעים, ויוצאים קצת אחרים. הבחירה בשם "הוטל מוגדור” היא כבר הצהרה. מלון = מקום מעבר, לא בית קבוע, מוגדור = עיר נמל, תנועה, ערבוב תרבויות. כך</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>פטריק סבג Hotel Mogador</v>
       </c>
     </row>
@@ -553,24 +562,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>"ריק בחלל" מציג את המפגש החד בין עומק רגשי ומודעות עצמית לבין הפקה פופ אלקטרונית עכשווית. השיר שעל שמו האלבום – מתקיים כל הזמן על הקצה: בין שליטה לאובדן, בין פגיעות לכוח, בין שקט פנימי לרעש חיצוני. זה לא שיר</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>מארינה מקסימיליאן – ריק בחלל</v>
       </c>
     </row>
@@ -588,24 +600,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>"אמנות האהבה" הוא אלבום האולפן השני של הזמרת האנגליה אוליביה דין .  זוהי אסופת שירים מלאי נשמה על אהבה, חיבור וצמיחה. התקליט, שמגיע אחרי אלבום הבכורה המהולל שלה, Messy, מציג את השילוב הייחודי של אוליביה דין בין ניאו-סול, פופ ו-R&amp;B,</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>אוליביה דין The Art of Loving</v>
       </c>
     </row>
@@ -623,24 +638,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>“יש פצצה באוטו שלי!” צורח קמרון וינטר. ברוכים הבאים להתקף הפאניקה שבסיוט הקדחתני שנקרא החיים בשנת 2025 — ול־‘Getting Killed’ של Geese. אלבום השנה בארים ובמגזיני רקו רבים. מי הזמין את הפיצוץ האבסורדי והפואטי הזה של ג’אז, פאנק רוק ורעש</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>Geese Getting Killed</v>
       </c>
     </row>
@@ -658,24 +676,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>הביטוי "מוזיקה היא הדת שלי" מופיע לעתים קרובות על מדבקות פגושיםשל מכוניות. עם זאת, באלבומה הרביעי LUX, הזמרת-יוצרת הספרדייה רוסליה הופכת את ההצהרה הזו להצהרה של רוחניות. הצלילים הגבוהים האופראיים של האלבום, העיבודים התזמורתיים והשימוש ב-13 שפות מוכיחים שההצהרה "מוזיקה</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>רוסליה Lux</v>
       </c>
     </row>
@@ -693,24 +714,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>לאחר הופעת מחווה איקונית בטקס פרסי ה-VMA של 2025, אגדת הרוק אירוסמית' Aerosmith מתאחדת עם הכוכב העולה יאנגבלאד YUNGBLUD למיני-אלבום בן 5 השירים, מפגן שירה של סטיבן טיילר וינגבלאד לכל אורכו, כולל 4 שירים חדשים שנכתבו על ידי סטיבן טיילר,</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>יאנגבלאד אירוסמית' one more time</v>
       </c>
     </row>
@@ -728,24 +752,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>כמה היינו רוצים להיות שם,  אי שם ב-1975, ולהאזין שוב ליצירת המופת של פינק פלויד "Wish You Were Here" כיצירה חדשה בפעם הראשונה, במקום לשמוע אותה דרך 50 שנות ראייה לאחור,  אבל גם ראיית הלאחור לא רעה, במיוחד אם זה</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>פינק פלויד Wish You Were Here 50</v>
       </c>
     </row>
@@ -763,24 +790,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>האלבום מתעד את ההופעה של דפש מוד בבירת מקסיקו במסגרת סיבוב ההופעות העולמי שליווה את אלבום האולפן האחרון ועטור השבחים של הלהקה, Memento Mori. האלבום מכיל 24 שירים + 4 שירי בונוס מתוך סשני האלבום Memento Mori, כך שהוא משלב</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>דפש מוד Memento Mori הופעה חיה במקסיקו</v>
       </c>
     </row>
@@ -798,24 +828,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>ה–EP טיפס השבוע לראש מצעד האלבומים של Billboard 200 בארצות הברית. זו הפעם השמינית ברציפות שכל אלבום/EP של Stray Kids, הלהקה הקוראנית,  מגיעה למקום הראשון – הישג חסר תקדים בהיסטוריה של המצעדים. ההצלחה מראה שהקהל האמריקאי (ובכלל הגלובלי) לא מגביל</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>סטריי קידס DO IT (EP)</v>
       </c>
     </row>
@@ -833,24 +866,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>דויד ברוזה אינו זמר ג'אז. ברוזה הוא אמן רב יוזמות, צבעים וניסיונות להתחדש, אבל לא אמן שהג'אז טבוע בעורקיו וביצירתו. האלבום הזה המכיל מיטב משיריו מתיימר להיות אלבום ג'אז. הוא לא. כלומר: חובבי ג'אז הרדקור לא ימצאו בו ערך מוסף</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>דויד ברוזה BROZAJAZZ</v>
       </c>
     </row>
@@ -868,24 +904,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>יותר מעשור לאחר שפרצו לסצנת הפופ, Five Seconds of Summer האוסטרלים חוזרים – לא  קאמבק כשלעצמו, אלא אלבום מגוון שסוף סוף מרגיש כאילו הוא שייך להם לחלוטין. הלהקה צמחה מחברים מקומיים מהתיכון באוסטרליה לאחת הלהקות המצליחות ביותר של המאה ה-21</v>
       </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>Five Seconds of Summer – Everyone's A Star</v>
       </c>
     </row>
@@ -903,24 +942,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>יש הרבה אור בחדש של "התקווה 6". הנה באים אלינו סימנים של גאולה ואיתם ניצוצות של התחלה חדשה, אומר אחד שירים. עוד מעט נחליף את הדמעות מעצב לשמח,  נוכל סוך סוף לבכות מהתרגשות גדולה. "התקווה 6" מדברת בשם קולקטיב ישראלי</v>
       </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>התקווה 6 – ויהי אור</v>
       </c>
     </row>
@@ -938,24 +980,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>האלבום הוא ביטוי של הישרדות פיזית ונפשית, בהפקה משלבת דרמטיות עם שלווה. הוא נוצר אחרי תקופה קשה בחייה של המובילה, פלורנס וולש Florence Welch, כולל ניתוח חירום בעקבות הריון חוץ-רחמי. העיסוק שלה ביצירה עובר הליך של תימצות חוויות של כאב,</v>
       </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>פלורנס אנד דה משין Everybody Scream</v>
       </c>
     </row>
@@ -973,24 +1018,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>אם באלבומים קודמים הדגש של טיים אימפלה היה על פסיכדליה רוקית, גיטרות, ומלודיות, ב־Deadbeat (אלבומה החמישי) בולט  שימוש בביטים אלקטרוניים, סינת’ים חזקים, לופים דיגיטליים. ההפקה הדיגיטלית הדומיננטית משקפת אולי את הרצון “לברוח” או “לעוף” מתוך המציאות. : האלבום מתמודד עם</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>טיים אימפלה Deadbeat</v>
       </c>
     </row>
@@ -1008,24 +1056,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
         <v>כדי לחגוג את סיבוב הסולד אאוט של Luck and Strange שלו ב-2024, דיוויד גילמור מוציא את אלבום ההופעות השלישי שלו, The Luck and Strange Concerts. האלבום כולל הופעות מסדרה מוגבלת של הופעות ברומא, לונדון, לוס אנג'לס וניו יורק, שירים מאלבום</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>דייוויד גילמור The Luck and Strange Concerts</v>
       </c>
     </row>
@@ -1043,24 +1094,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
         <v>12 שנה חיכינו לאלבום חדש של שלמה גרוניך. 11 שירים חדשים מחזירים את היוצר המופלא הזה לימיו הטובים. חלק מהשירים נכתבו בעקבות השבעה באוקטובר בחיפוש אחר חידוש האמונה באדם. השיר הראשון באלבום, "זריחת האדם", ובו המילים "ראה עוד נראה את</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>שלמה גרוניך – תודה אהבה</v>
       </c>
     </row>
@@ -1078,24 +1132,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
         <v>טיילור סוויפט אינה רק זמרת – היא תופעה תרבותית. במהלך יותר מעשור בתעשיית המוזיקה, טיילור הפכה מדמות חמודה בקאנטרי פופ לאייקון גלובלי, שמופעיה נראים יותר כהפקות תיאטרון גרנדיוזיות מאשר "רק" הופעות מוזיקליות. הופעותיה במופע "The Eras Tour" הציבו רף חדש</v>
       </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>טיילור סוויפט The Life Of A Showgirl</v>
       </c>
     </row>
@@ -1113,24 +1170,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
         <v>אהבה, רומנטיקה, התשוקה והקשר בין בני זוג, תחושת חוסר ודאות, קנאה, משיכה וניגודים רגשיים, מערכות יחסים עם העצמי. דוג'ה קאט Doja Cat – אלבומה החמישי. קאט אמרה כי זה פרויקט שמנגיש  את צד הפופ שלה, לאחר שבתקופה מסוימת טענה שהיא “לא</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>דוג'ה קאט Vie</v>
       </c>
     </row>
@@ -1148,24 +1208,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
         <v>"Juniper" הוא אלבומה השני של הזמרת-יוצרת הבריטית ג'וי קרוקס. האלבום הוא גוף יצירה אישי ורגשי שצמח לאחר תקופה של טלטלה אישית, כולל משבר נפשי. הוא כולל נושאים של זהות, חרדה, מערכות יחסים וגילוי עצמי, עם הופעות אורח של וינס סטייפלס</v>
       </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>ג'וי קרוקס Juniper</v>
       </c>
     </row>
@@ -1183,24 +1246,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
         <v>ביפי קליירו  Biffy Clyro היא להקת רוק אלטרנטיבי מסקוטלנד, שנחשבת לאחת מהלהקות הבולטות בז'אנר הרוק הבריטי של שנות ה-2000 וה-2010. הלהקה היא שילוב בין רוק אלטרנטיבי, פוסט-הרדקור, פרוגרסיב רוק ואינדי רוק. הם מרבים לשלב שירים עם מקצבים לא שגרתיים, מעברים</v>
       </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>ביפי קליירו Futique</v>
       </c>
     </row>
@@ -1218,24 +1284,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
         <v>Play מסמן מעבר מנוסחה קודמת של Ed (“Mathematics series”) לסדרה חדשה של אלבומים עם סמלים – Play, Pause, Rewind, Stop וכו’. אחד המאפיינים הבולטים של Play הוא הטמעה של מרכיבים מוזיקליים ממזרח ומפרס. דוגמה בולטת: השיר "Azizam", שמתקשר לפרסית, ומשלב</v>
       </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>אד שירן Play</v>
       </c>
     </row>
@@ -1253,24 +1322,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
         <v>האלבום של עידן רייכל והפרויקט נפתח ב"האהבה שלי" – שיר כאוב, עמוק ואינטימי שמשרטט תמונה מורכבת של אהבה הרוסה, אכזבה, ושבר פנימי – לצד כמיהה לתיקון ולריפוי. יש כאן תיאור של מישהי שנשברה – אולי נפשית, אולי רגשית – והמספר</v>
       </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>הפרויקט של עידן רייכל – עד סוף העולם</v>
       </c>
     </row>
@@ -1288,24 +1360,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
         <v>Antidepressants, אלבום האולפן העשירי של סוויד (Suede), הוא הישג משמעותי שמעמיד את הלהקה בפסגת להקות הרוק האיכותיות נכון להיום.  האלבום מגיע לאחר הצלחת אלבומה התשיעי,"Autofiction", שזכה לשבחי המבקרים,  שיצא בספטמבר 2022, והגיע למקום השני במצעד האלבומים הבריטי. זהו אלבום שעושה</v>
       </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>סוויד Antidepressants</v>
       </c>
     </row>
@@ -1323,24 +1398,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
         <v>The Clearing של וולף אליס Wolf Alice הוא אלבום האולפן הרביעי של להקת הרוק האנגלית שמגיע ברגע של התגבשות עבור אחת הלהקות החדשניות והטעונות רגשית ביותר בבריטניה. The Clearing, שהוקלט בלוס אנג'לס עם המפיק זוכה הגראמי גרג קורסטין, הוא מקבץ</v>
       </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>וולף אליס The Clearing</v>
       </c>
     </row>
@@ -1358,24 +1436,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
         <v>איזה משב רוח רענן עבר על השירים של אהוד בנאי. עלה על ספינה שיצאה מג'מייקה בפיקודו של רב החובל בנו הנדלר והגיעה לחופי הארץ. הסגנון – דאב. כן, כן זה הסגנון שינק מהרגאי של ג'מייקה?  כדי להתאהב מחדש באהוד בנאי</v>
       </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>אהוד בנאי ובנו הנדלר פליטי הדאב</v>
       </c>
     </row>
@@ -1393,24 +1474,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
         <v>האלבום בן 15 השירים זה משלב את שירת הנשמה הייחודית של טום גרנן עם המנוני פופ אנרגטיים בהפקתו של יוצר ג'סטין טרנטר (דואה ליפה, בריטני ספירס).  גרנן עשה כברת דרך ארוכה מאז ימיו בהופעותיו בפאבים קטנים בלונדון עם גיטרה אקוסטית</v>
       </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>טום גרנן Everywhere I Went Led Me To Where I Didn'T Want To Be</v>
       </c>
     </row>
@@ -1428,24 +1512,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
         <v>עם 10 שירים ומשך כולל של כ־28 דקות – זה האלבום הקצר ביותר של טיילר דה קריאטור,  אך בשונה מ־Chromakopia (2024), שהיה עמוק ומושתת על קונספט, כאן Tyler מעדיף אווירה ויזואלית ואנרגיה. טיילר דה קריאטור (Tyler, The Creator) הוא אחת</v>
       </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J30" t="str">
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>טיילר דה קריאייטור Don't Tap The Glass</v>
       </c>
     </row>
@@ -1463,30 +1550,33 @@
         <v>2026-01-22</v>
       </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v>"יחפים על הדשא" שפותח את האלבום של אברהם טל מתאר דרך זיכרון אישי חוויות של אהבה, תמימות, כאב, ומאבק פנימי. מתחת לפשטות הלשונית מסתתר עומק רגשי חזק, עם נוכחות של אהבה גדולה שמלווה גם בתקופות קשות של התמודדות עצמית. זה</v>
       </c>
-      <c r="F31" t="str">
-        <v/>
-      </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>אלבומים חדשים</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>אברהם טל – חי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-01-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99-%d7%95%d7%99%d7%9c%d7%99%d7%90%d7%9e%d7%a1-britpop/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E31" t="str">
         <v/>

--- a/data/tags/אלבומים חדשים/sites/yosmusic/2026-01-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/yosmusic/2026-01-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99-%d7%95%d7%99%d7%9c%d7%99%d7%90%d7%9e%d7%a1-britpop/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://yosmusic.com/%d7%a2%d7%95%d7%96-%d7%96%d7%94%d7%91%d7%99-%d7%aa%d7%95%d7%a8-%d7%96%d7%94%d7%91%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%98%d7%a8%d7%99%d7%a7-%d7%a1%d7%91%d7%92-hotel-mogador/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://yosmusic.com/%d7%9e%d7%90%d7%a8%d7%99%d7%a0%d7%94-%d7%9e%d7%a7%d7%a1%d7%99%d7%9e%d7%99%d7%9c%d7%99%d7%90%d7%9f-%d7%a8%d7%99%d7%a7-%d7%91%d7%97%d7%9c%d7%9c-2/</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://yosmusic.com/%d7%90%d7%95%d7%9c%d7%99%d7%91%d7%99%d7%94-%d7%93%d7%99%d7%9f-the-art-of-loving/</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://yosmusic.com/geese-getting-killed/</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://yosmusic.com/%d7%a8%d7%95%d7%a1%d7%9c%d7%99%d7%94-lux/</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://yosmusic.com/%d7%99%d7%90%d7%a0%d7%92%d7%91%d7%9c%d7%90%d7%93-%d7%90%d7%99%d7%a8%d7%95%d7%a1%d7%9e%d7%99%d7%aa-one-more-time/</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%99%d7%a0%d7%a7-%d7%a4%d7%9c%d7%95%d7%99%d7%93-wish-you-were-here-50/</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://yosmusic.com/%d7%93%d7%a4%d7%a9-%d7%9e%d7%95%d7%93-memento-mori-%d7%94%d7%95%d7%a4%d7%a2%d7%94-%d7%97%d7%99%d7%94-%d7%91%d7%9e%d7%a7%d7%a1%d7%99%d7%a7%d7%95/</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%98%d7%a8%d7%99%d7%99-%d7%a7%d7%99%d7%93%d7%a1-do-it-ep/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%99%d7%93-%d7%91%d7%a8%d7%95%d7%96%d7%94-brozajazz/</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://yosmusic.com/five-seconds-of-summer-everyones-a-star/</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%95%d7%99%d7%94%d7%99-%d7%90%d7%95%d7%a8-2/</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://yosmusic.com/%d7%a4%d7%9c%d7%95%d7%a8%d7%a0%d7%a1-%d7%90%d7%a0%d7%93-%d7%93%d7%94-%d7%9e%d7%a9%d7%99%d7%9f-everybody-scream/</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9d-%d7%90%d7%99%d7%9e%d7%a4%d7%9c%d7%94-deadbeat/</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://yosmusic.com/%d7%93%d7%99%d7%99%d7%95%d7%95%d7%99%d7%93-%d7%92%d7%99%d7%9c%d7%9e%d7%95%d7%a8-the-luck-and-strange-concerts/</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://yosmusic.com/%d7%a9%d7%9c%d7%9e%d7%94-%d7%92%d7%a8%d7%95%d7%a0%d7%99%d7%9a-%d7%aa%d7%95%d7%93%d7%94-%d7%90%d7%94%d7%91%d7%94/</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%95%d7%a8-%d7%a1%d7%95%d7%95%d7%99%d7%a4%d7%98-the-life-of-a-showgirl/</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://yosmusic.com/%d7%93%d7%95%d7%92%d7%94-%d7%a7%d7%90%d7%98-vie/</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://yosmusic.com/%d7%92%d7%95%d7%99-%d7%a7%d7%a8%d7%95%d7%a7%d7%a1-juniper/</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://yosmusic.com/%d7%91%d7%99%d7%a4%d7%99-%d7%a7%d7%9c%d7%99%d7%99%d7%a8%d7%95-futique/</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://yosmusic.com/%d7%90%d7%93-%d7%a9%d7%99%d7%a8%d7%9f-play/</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%a2%d7%99%d7%93%d7%9f-%d7%a8%d7%99%d7%99%d7%9b%d7%9c-%d7%a2%d7%93-%d7%a1%d7%95%d7%a3-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://yosmusic.com/%d7%a1%d7%95%d7%95%d7%99%d7%93-antidepressants/</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://yosmusic.com/%d7%95%d7%95%d7%9c%d7%a3-%d7%90%d7%9c%d7%99%d7%a1-the-clearing/</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://yosmusic.com/%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%95%d7%91%d7%a0%d7%95-%d7%94%d7%a0%d7%93%d7%9c%d7%a8-%d7%a4%d7%9c%d7%99%d7%98%d7%99-%d7%94%d7%93%d7%90%d7%91/</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://yosmusic.com/%d7%98%d7%95%d7%9d-%d7%92%d7%a8%d7%a0%d7%9f-everywhere-i-went-led-me-to-where-i-didnt-want-to-be/</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://yosmusic.com/%d7%98%d7%99%d7%99%d7%9c%d7%a8-%d7%93%d7%94-%d7%a7%d7%a8%d7%99%d7%90%d7%99%d7%99%d7%98%d7%95%d7%a8-dont-tap-the-glass/</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%97%d7%99/</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
